--- a/louvers/files/reference_xls/price_xls/fluted.xlsx
+++ b/louvers/files/reference_xls/price_xls/fluted.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10110"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10308"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/snigdhagoel/Documents/Vibrant Technik/vibrant-technik/offer-generator/files/reference_xls/price_xls/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/snigdhagoel/Documents/Vibrant Technik/vibrant-technik/offer-generator-test/louvers/files/reference_xls/price_xls/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6A1EF3E-AFCF-CF4C-88BE-7C9DE72A3CFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A2330B8-F67A-8A45-86BB-EFB7C242A79C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="28800" windowHeight="15940" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -878,12 +878,12 @@
       </c>
       <c r="B2" s="31">
         <f>+(D2/(39.37*5.83))*144</f>
-        <v>762.26293104387241</v>
+        <v>838.48922414825961</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="32">
         <f>1.62*$A$7</f>
-        <v>1215</v>
+        <v>1336.5</v>
       </c>
       <c r="E2" s="24">
         <v>142</v>
@@ -906,30 +906,30 @@
       </c>
       <c r="B3" s="31">
         <f t="shared" ref="B3:B4" si="0">+(D3/(39.37*5.83))*144</f>
-        <v>762.26293104387241</v>
+        <v>838.48922414825961</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="32">
         <f t="shared" ref="D3:D4" si="1">1.62*$A$7</f>
-        <v>1215</v>
+        <v>1336.5</v>
       </c>
       <c r="E3" s="24">
         <f>E2+B3</f>
-        <v>904.26293104387241</v>
+        <v>980.48922414825961</v>
       </c>
       <c r="F3" s="18"/>
       <c r="G3" s="26">
         <f>G2+D2</f>
-        <v>1420.2</v>
+        <v>1541.7</v>
       </c>
       <c r="H3" s="25">
         <f>H2+B3</f>
-        <v>1018.2629310438724</v>
+        <v>1094.4892241482596</v>
       </c>
       <c r="I3" s="19"/>
       <c r="J3" s="28">
         <f>J2+D3</f>
-        <v>1707.5</v>
+        <v>1829</v>
       </c>
     </row>
     <row r="4" spans="1:10" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -938,30 +938,30 @@
       </c>
       <c r="B4" s="33">
         <f t="shared" si="0"/>
-        <v>762.26293104387241</v>
+        <v>838.48922414825961</v>
       </c>
       <c r="C4" s="5"/>
       <c r="D4" s="34">
         <f t="shared" si="1"/>
-        <v>1215</v>
+        <v>1336.5</v>
       </c>
       <c r="E4" s="6">
         <f>(E2*2)+B4</f>
-        <v>1046.2629310438724</v>
+        <v>1122.4892241482596</v>
       </c>
       <c r="F4" s="7"/>
       <c r="G4" s="27">
         <f>(G2*2)+D4</f>
-        <v>1625.4</v>
+        <v>1746.9</v>
       </c>
       <c r="H4" s="8">
         <f>(H2*2)+B4</f>
-        <v>1274.2629310438724</v>
+        <v>1350.4892241482596</v>
       </c>
       <c r="I4" s="9"/>
       <c r="J4" s="10">
         <f>(J2*2)+D4</f>
-        <v>2200</v>
+        <v>2321.5</v>
       </c>
     </row>
     <row r="5" spans="1:10" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
@@ -973,7 +973,7 @@
     </row>
     <row r="7" spans="1:10" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A7" s="23">
-        <v>750</v>
+        <v>825</v>
       </c>
     </row>
   </sheetData>
